--- a/data/Data Service Type.xlsx
+++ b/data/Data Service Type.xlsx
@@ -61,7 +61,7 @@
     <t>Pawship Timur,Pawship Barat</t>
   </si>
   <si>
-    <t>ADD-ON</t>
+    <t>ADDONS</t>
   </si>
 </sst>
 </file>
